--- a/event_registration_forms/016_relay_team_expression_of_interest--event_registration_forms.xlsx
+++ b/event_registration_forms/016_relay_team_expression_of_interest--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'swimming'}</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Swimming'}</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cycling'}</t>
+          <t>cycling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cycling'}</t>
+          <t>Cycling</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'running'}</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Running'}</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'triathlon'}</t>
+          <t>triathlon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Triathlon'}</t>
+          <t>Triathlon</t>
         </is>
       </c>
     </row>
@@ -1233,301 +1233,250 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'rowing'}</t>
+          <t>rowing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Rowing'}</t>
+          <t>Rowing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>available_sport_choices</t>
+          <t>interested_in_coaching_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'rowing'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Rowing'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>available_sport_choices</t>
+          <t>interested_in_coaching_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'rowing'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Rowing'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>available_sport_choices</t>
+          <t>interested_in_coaching_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'rowing'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Rowing'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>interested_in_coaching_choices</t>
+          <t>team_sport_coach_experience_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>interested_in_coaching_choices</t>
+          <t>team_sport_coach_experience_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>interested_in_coaching_choices</t>
+          <t>available_coaching_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'undecided'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Undecided'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>team_sport_coach_experience_choices</t>
+          <t>available_coaching_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_sport_coach_experience_choices</t>
+          <t>available_coaching_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>available_coaching_choices</t>
+          <t>team_sport_coaching_experience_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>available_coaching_choices</t>
+          <t>team_sport_coaching_experience_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>available_coaching_choices</t>
+          <t>available_team_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'undecided'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Undecided'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>team_sport_coaching_experience_choices</t>
+          <t>available_team_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>team_sport_coaching_experience_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>available_team_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>available_team_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>team_lead_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>team_lead_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
